--- a/uploads/Tulip Yellow.xlsx
+++ b/uploads/Tulip Yellow.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="524">
   <si>
     <t>Owner/  Occupier Name (D)</t>
   </si>
@@ -1548,6 +1548,66 @@
   <si>
     <t xml:space="preserve">
 </t>
+  </si>
+  <si>
+    <t>Address of Property (K)</t>
+  </si>
+  <si>
+    <t>DUPLICATE NO.</t>
+  </si>
+  <si>
+    <t>DUPLICATE NO .</t>
+  </si>
+  <si>
+    <t>CALL BUSY</t>
+  </si>
+  <si>
+    <t>PRICE 2.30 CR</t>
+  </si>
+  <si>
+    <t>DUPLICATEN NO .</t>
+  </si>
+  <si>
+    <t>DUPLICATE NO ,</t>
+  </si>
+  <si>
+    <t>DUPLI</t>
+  </si>
+  <si>
+    <t>TULIP KE PASS UNIT H</t>
+  </si>
+  <si>
+    <t>,, ,, ,, ,,,</t>
+  </si>
+  <si>
+    <t>WRONG NO</t>
+  </si>
+  <si>
+    <t>WRONG NO.</t>
+  </si>
+  <si>
+    <t>WRONG NO .</t>
+  </si>
+  <si>
+    <t>WRONG NO </t>
+  </si>
+  <si>
+    <t>TULIP KE PASS H</t>
+  </si>
+  <si>
+    <t>BROKER</t>
+  </si>
+  <si>
+    <t>wrong no .</t>
+  </si>
+  <si>
+    <t>TULIP KE PASSS UNIT H</t>
+  </si>
+  <si>
+    <t>SWICH OFF</t>
+  </si>
+  <si>
+    <t>WRONG NI .</t>
   </si>
 </sst>
 </file>
@@ -1927,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4067,6 +4127,9 @@
       <c r="D128" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E128" t="s" s="0">
+        <v>505</v>
+      </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s" s="0">
@@ -4081,6 +4144,9 @@
       <c r="D129" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E129" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s" s="0">
@@ -4095,6 +4161,9 @@
       <c r="D130" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E130" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s" s="0">
@@ -4109,6 +4178,9 @@
       <c r="D131" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E131" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s" s="0">
@@ -4122,6 +4194,9 @@
       </c>
       <c r="D132" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E132" t="s" s="0">
+        <v>506</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -4137,6 +4212,9 @@
       <c r="D133" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E133" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s" s="0">
@@ -4151,6 +4229,9 @@
       <c r="D134" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E134" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s" s="0">
@@ -4165,6 +4246,9 @@
       <c r="D135" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E135" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s" s="0">
@@ -4178,6 +4262,9 @@
       </c>
       <c r="D136" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E136" t="s" s="0">
+        <v>506</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -4193,6 +4280,9 @@
       <c r="D137" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E137" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s" s="0">
@@ -4207,6 +4297,9 @@
       <c r="D138" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E138" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s" s="0">
@@ -4221,6 +4314,9 @@
       <c r="D139" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E139" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s" s="0">
@@ -4235,6 +4331,9 @@
       <c r="D140" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E140" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s" s="0">
@@ -4248,6 +4347,9 @@
       </c>
       <c r="D141" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E141" t="s" s="0">
+        <v>506</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -4263,6 +4365,9 @@
       <c r="D142" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E142" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s" s="0">
@@ -4276,6 +4381,9 @@
       </c>
       <c r="D143" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E143" t="s" s="0">
+        <v>506</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -4291,6 +4399,9 @@
       <c r="D144" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E144" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s" s="0">
@@ -4305,6 +4416,9 @@
       <c r="D145" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E145" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s" s="0">
@@ -4319,6 +4433,9 @@
       <c r="D146" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E146" t="s" s="0">
+        <v>506</v>
+      </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s" s="0">
@@ -4333,6 +4450,9 @@
       <c r="D147" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E147" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s" s="0">
@@ -4346,6 +4466,9 @@
       </c>
       <c r="D148" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E148" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -4361,6 +4484,9 @@
       <c r="D149" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E149" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s" s="0">
@@ -4375,6 +4501,9 @@
       <c r="D150" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E150" t="s" s="0">
+        <v>515</v>
+      </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s" s="0">
@@ -4389,6 +4518,9 @@
       <c r="D151" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E151" t="s" s="0">
+        <v>515</v>
+      </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s" s="0">
@@ -4403,6 +4535,9 @@
       <c r="D152" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E152" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s" s="0">
@@ -4417,6 +4552,9 @@
       <c r="D153" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E153" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s" s="0">
@@ -4430,6 +4568,9 @@
       </c>
       <c r="D154" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E154" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
@@ -4445,6 +4586,9 @@
       <c r="D155" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E155" t="s" s="0">
+        <v>517</v>
+      </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s" s="0">
@@ -4459,6 +4603,9 @@
       <c r="D156" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E156" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s" s="0">
@@ -4472,6 +4619,9 @@
       </c>
       <c r="D157" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E157" t="s" s="0">
+        <v>514</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -4487,6 +4637,9 @@
       <c r="D158" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E158" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s" s="0">
@@ -4500,6 +4653,9 @@
       </c>
       <c r="D159" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E159" t="s" s="0">
+        <v>514</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
@@ -4515,6 +4671,9 @@
       <c r="D160" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E160" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s" s="0">
@@ -4529,6 +4688,9 @@
       <c r="D161" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E161" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s" s="0">
@@ -4542,6 +4704,9 @@
       </c>
       <c r="D162" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E162" t="s" s="0">
+        <v>518</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -4557,6 +4722,9 @@
       <c r="D163" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E163" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s" s="0">
@@ -4571,6 +4739,9 @@
       <c r="D164" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E164" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s" s="0">
@@ -4585,6 +4756,9 @@
       <c r="D165" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E165" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s" s="0">
@@ -4599,6 +4773,9 @@
       <c r="D166" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E166" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s" s="0">
@@ -4612,6 +4789,9 @@
       </c>
       <c r="D167" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E167" t="s" s="0">
+        <v>514</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -4627,6 +4807,9 @@
       <c r="D168" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E168" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s" s="0">
@@ -4641,6 +4824,9 @@
       <c r="D169" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E169" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s" s="0">
@@ -4655,6 +4841,9 @@
       <c r="D170" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E170" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s" s="0">
@@ -4669,6 +4858,9 @@
       <c r="D171" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E171" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s" s="0">
@@ -4682,6 +4874,9 @@
       </c>
       <c r="D172" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E172" t="s" s="0">
+        <v>514</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -4697,6 +4892,9 @@
       <c r="D173" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E173" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s" s="0">
@@ -4711,6 +4909,9 @@
       <c r="D174" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E174" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s" s="0">
@@ -4725,6 +4926,9 @@
       <c r="D175" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E175" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s" s="0">
@@ -4739,6 +4943,9 @@
       <c r="D176" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E176" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s" s="0">
@@ -4752,6 +4959,9 @@
       </c>
       <c r="D177" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E177" t="s" s="0">
+        <v>514</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -4767,6 +4977,9 @@
       <c r="D178" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E178" t="s" s="0">
+        <v>519</v>
+      </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s" s="0">
@@ -4781,6 +4994,9 @@
       <c r="D179" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E179" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s" s="0">
@@ -4794,6 +5010,9 @@
       </c>
       <c r="D180" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E180" t="s" s="0">
+        <v>514</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
@@ -4809,6 +5028,9 @@
       <c r="D181" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E181" t="s" s="0">
+        <v>518</v>
+      </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s" s="0">
@@ -4823,6 +5045,9 @@
       <c r="D182" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E182" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s" s="0">
@@ -4836,6 +5061,9 @@
       </c>
       <c r="D183" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E183" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
@@ -4851,6 +5079,9 @@
       <c r="D184" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E184" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s" s="0">
@@ -4865,6 +5096,9 @@
       <c r="D185" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E185" t="s" s="0">
+        <v>515</v>
+      </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s" s="0">
@@ -4879,6 +5113,9 @@
       <c r="D186" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E186" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s" s="0">
@@ -4893,6 +5130,9 @@
       <c r="D187" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E187" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s" s="0">
@@ -4906,6 +5146,9 @@
       </c>
       <c r="D188" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E188" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
@@ -4921,6 +5164,9 @@
       <c r="D189" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E189" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s" s="0">
@@ -4935,6 +5181,9 @@
       <c r="D190" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E190" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s" s="0">
@@ -4949,6 +5198,9 @@
       <c r="D191" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E191" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s" s="0">
@@ -4962,6 +5214,9 @@
       </c>
       <c r="D192" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E192" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -4977,6 +5232,9 @@
       <c r="D193" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E193" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s" s="0">
@@ -4991,6 +5249,9 @@
       <c r="D194" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E194" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s" s="0">
@@ -5004,6 +5265,9 @@
       </c>
       <c r="D195" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E195" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
@@ -5019,6 +5283,9 @@
       <c r="D196" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E196" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s" s="0">
@@ -5033,6 +5300,9 @@
       <c r="D197" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E197" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s" s="0">
@@ -5047,6 +5317,9 @@
       <c r="D198" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E198" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s" s="0">
@@ -5061,6 +5334,9 @@
       <c r="D199" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E199" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s" s="0">
@@ -5075,6 +5351,9 @@
       <c r="D200" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E200" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s" s="0">
@@ -5089,6 +5368,9 @@
       <c r="D201" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E201" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s" s="0">
@@ -5103,6 +5385,9 @@
       <c r="D202" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E202" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s" s="0">
@@ -5117,6 +5402,9 @@
       <c r="D203" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E203" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s" s="0">
@@ -5130,6 +5418,9 @@
       </c>
       <c r="D204" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E204" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -5145,6 +5436,9 @@
       <c r="D205" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E205" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s" s="0">
@@ -5158,6 +5452,9 @@
       </c>
       <c r="D206" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E206" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -5173,6 +5470,9 @@
       <c r="D207" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E207" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s" s="0">
@@ -5187,6 +5487,9 @@
       <c r="D208" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E208" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s" s="0">
@@ -5201,6 +5504,9 @@
       <c r="D209" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E209" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s" s="0">
@@ -5215,6 +5521,9 @@
       <c r="D210" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E210" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s" s="0">
@@ -5229,6 +5538,9 @@
       <c r="D211" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E211" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s" s="0">
@@ -5242,6 +5554,9 @@
       </c>
       <c r="D212" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E212" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -5257,6 +5572,9 @@
       <c r="D213" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E213" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s" s="0">
@@ -5270,6 +5588,9 @@
       </c>
       <c r="D214" s="0">
         <v>1831.98</v>
+      </c>
+      <c r="E214" t="s" s="0">
+        <v>516</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -5285,6 +5606,9 @@
       <c r="D215" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E215" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s" s="0">
@@ -5299,6 +5623,9 @@
       <c r="D216" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E216" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s" s="0">
@@ -5312,6 +5639,9 @@
       </c>
       <c r="D217" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E217" t="s" s="0">
+        <v>521</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -5327,6 +5657,9 @@
       <c r="D218" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E218" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s" s="0">
@@ -5341,6 +5674,9 @@
       <c r="D219" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E219" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s" s="0">
@@ -5354,6 +5690,9 @@
       </c>
       <c r="D220" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E220" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -5369,6 +5708,9 @@
       <c r="D221" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E221" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s" s="0">
@@ -5382,6 +5724,9 @@
       </c>
       <c r="D222" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E222" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -5397,6 +5742,9 @@
       <c r="D223" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E223" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s" s="0">
@@ -5411,6 +5759,9 @@
       <c r="D224" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E224" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s" s="0">
@@ -5424,6 +5775,9 @@
       </c>
       <c r="D225" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E225" t="s" s="0">
+        <v>521</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -5439,6 +5793,9 @@
       <c r="D226" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E226" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s" s="0">
@@ -5453,6 +5810,9 @@
       <c r="D227" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E227" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s" s="0">
@@ -5467,6 +5827,9 @@
       <c r="D228" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E228" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s" s="0">
@@ -5481,6 +5844,9 @@
       <c r="D229" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E229" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s" s="0">
@@ -5495,6 +5861,9 @@
       <c r="D230" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E230" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s" s="0">
@@ -5509,6 +5878,9 @@
       <c r="D231" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E231" t="s" s="0">
+        <v>521</v>
+      </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s" s="0">
@@ -5522,6 +5894,9 @@
       </c>
       <c r="D232" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E232" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -5537,6 +5912,9 @@
       <c r="D233" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E233" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s" s="0">
@@ -5550,6 +5928,9 @@
       </c>
       <c r="D234" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E234" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -5565,6 +5946,9 @@
       <c r="D235" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E235" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s" s="0">
@@ -5579,6 +5963,9 @@
       <c r="D236" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E236" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s" s="0">
@@ -5593,6 +5980,9 @@
       <c r="D237" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E237" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s" s="0">
@@ -5606,6 +5996,9 @@
       </c>
       <c r="D238" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E238" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -5621,6 +6014,9 @@
       <c r="D239" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E239" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s" s="0">
@@ -5635,6 +6031,9 @@
       <c r="D240" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E240" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s" s="0">
@@ -5649,6 +6048,9 @@
       <c r="D241" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E241" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s" s="0">
@@ -5663,6 +6065,9 @@
       <c r="D242" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E242" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s" s="0">
@@ -5676,6 +6081,9 @@
       </c>
       <c r="D243" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E243" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -5691,6 +6099,9 @@
       <c r="D244" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E244" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s" s="0">
@@ -5705,6 +6116,9 @@
       <c r="D245" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E245" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s" s="0">
@@ -5719,6 +6133,9 @@
       <c r="D246" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E246" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s" s="0">
@@ -5760,6 +6177,9 @@
       </c>
       <c r="D249" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E249" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -5775,6 +6195,9 @@
       <c r="D250" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E250" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s" s="0">
@@ -5789,6 +6212,9 @@
       <c r="D251" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E251" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s" s="0">
@@ -5803,6 +6229,9 @@
       <c r="D252" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E252" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s" s="0">
@@ -5816,6 +6245,9 @@
       </c>
       <c r="D253" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E253" t="s" s="0">
+        <v>521</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
@@ -5831,6 +6263,9 @@
       <c r="D254" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E254" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s" s="0">
@@ -5845,6 +6280,9 @@
       <c r="D255" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E255" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s" s="0">
@@ -5859,6 +6297,9 @@
       <c r="D256" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E256" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s" s="0">
@@ -5872,6 +6313,9 @@
       </c>
       <c r="D257" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E257" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -5887,6 +6331,9 @@
       <c r="D258" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E258" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s" s="0">
@@ -5900,6 +6347,9 @@
       </c>
       <c r="D259" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E259" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
@@ -5915,6 +6365,9 @@
       <c r="D260" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E260" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s" s="0">
@@ -5928,6 +6381,9 @@
       </c>
       <c r="D261" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E261" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -5943,6 +6399,9 @@
       <c r="D262" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E262" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s" s="0">
@@ -5956,6 +6415,9 @@
       </c>
       <c r="D263" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E263" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -5971,6 +6433,9 @@
       <c r="D264" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E264" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s" s="0">
@@ -5985,6 +6450,9 @@
       <c r="D265" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E265" t="s" s="0">
+        <v>494</v>
+      </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s" s="0">
@@ -5998,6 +6466,9 @@
       </c>
       <c r="D266" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E266" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -6013,6 +6484,9 @@
       <c r="D267" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E267" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s" s="0">
@@ -6027,6 +6501,9 @@
       <c r="D268" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E268" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s" s="0">
@@ -6040,6 +6517,9 @@
       </c>
       <c r="D269" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E269" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -6055,6 +6535,9 @@
       <c r="D270" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E270" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s" s="0">
@@ -6069,6 +6552,9 @@
       <c r="D271" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E271" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s" s="0">
@@ -6083,6 +6569,9 @@
       <c r="D272" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E272" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s" s="0">
@@ -6096,6 +6585,9 @@
       </c>
       <c r="D273" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E273" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -6111,6 +6603,9 @@
       <c r="D274" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E274" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s" s="0">
@@ -6125,6 +6620,9 @@
       <c r="D275" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E275" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s" s="0">
@@ -6138,6 +6636,9 @@
       </c>
       <c r="D276" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E276" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -6153,6 +6654,9 @@
       <c r="D277" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E277" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s" s="0">
@@ -6167,6 +6671,9 @@
       <c r="D278" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E278" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s" s="0">
@@ -6181,6 +6688,9 @@
       <c r="D279" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E279" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s" s="0">
@@ -6194,6 +6704,9 @@
       </c>
       <c r="D280" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E280" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
@@ -6209,6 +6722,9 @@
       <c r="D281" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E281" t="s" s="0">
+        <v>522</v>
+      </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s" s="0">
@@ -6223,6 +6739,9 @@
       <c r="D282" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E282" t="s" s="0">
+        <v>515</v>
+      </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s" s="0">
@@ -6237,6 +6756,9 @@
       <c r="D283" s="0">
         <v>1831.98</v>
       </c>
+      <c r="E283" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s" s="0">
@@ -6251,6 +6773,9 @@
       <c r="D284" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E284" t="s" s="0">
+        <v>514</v>
+      </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s" s="0">
@@ -6265,6 +6790,9 @@
       <c r="D285" s="0">
         <v>44.22</v>
       </c>
+      <c r="E285" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s" s="0">
@@ -6279,6 +6807,9 @@
       <c r="D286" s="0">
         <v>44.22</v>
       </c>
+      <c r="E286" t="s" s="0">
+        <v>521</v>
+      </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s" s="0">
@@ -6293,6 +6824,9 @@
       <c r="D287" s="0">
         <v>41.78</v>
       </c>
+      <c r="E287" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s" s="0">
@@ -6307,6 +6841,9 @@
       <c r="D288" s="0">
         <v>41.78</v>
       </c>
+      <c r="E288" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s" s="0">
@@ -6321,6 +6858,9 @@
       <c r="D289" s="0">
         <v>41.78</v>
       </c>
+      <c r="E289" t="s" s="0">
+        <v>521</v>
+      </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s" s="0">
@@ -6335,6 +6875,9 @@
       <c r="D290" s="0">
         <v>41.78</v>
       </c>
+      <c r="E290" t="s" s="0">
+        <v>512</v>
+      </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s" s="0">
@@ -6348,6 +6891,9 @@
       </c>
       <c r="D291" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E291" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -6363,6 +6909,9 @@
       <c r="D292" s="0">
         <v>1033.99</v>
       </c>
+      <c r="E292" t="s" s="0">
+        <v>516</v>
+      </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s" s="0">
@@ -6376,6 +6925,9 @@
       </c>
       <c r="D293" s="0">
         <v>1033.99</v>
+      </c>
+      <c r="E293" t="s" s="0">
+        <v>512</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
@@ -6391,6 +6943,9 @@
       <c r="D294" s="0">
         <v>1034.3</v>
       </c>
+      <c r="E294" t="s" s="0">
+        <v>511</v>
+      </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s" s="0">
@@ -6405,6 +6960,9 @@
       <c r="D295" s="0">
         <v>1034.3</v>
       </c>
+      <c r="E295" t="s" s="0">
+        <v>510</v>
+      </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s" s="0">
@@ -6419,6 +6977,9 @@
       <c r="D296" s="0">
         <v>1034.3</v>
       </c>
+      <c r="E296" t="s" s="0">
+        <v>509</v>
+      </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s" s="0">
@@ -6433,6 +6994,9 @@
       <c r="D297" s="0">
         <v>1034.3</v>
       </c>
+      <c r="E297" t="s" s="0">
+        <v>508</v>
+      </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s" s="0">
@@ -6447,6 +7011,9 @@
       <c r="D298" s="0">
         <v>1034.3</v>
       </c>
+      <c r="E298" t="s" s="0">
+        <v>507</v>
+      </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s" s="0">
@@ -6460,6 +7027,9 @@
       </c>
       <c r="D299" s="0">
         <v>1034.3</v>
+      </c>
+      <c r="E299" t="s" s="0">
+        <v>507</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
